--- a/output/pdf_financials_xlsx/SAGA.xlsx
+++ b/output/pdf_financials_xlsx/SAGA.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003037</v>
       </c>
     </row>
     <row r="13">
@@ -867,7 +867,7 @@
         <v>-1.174272</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.42199</v>
+        <v>-2.425027</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
         <v>-1.168853</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.405897</v>
+        <v>-2.408934</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.236341</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.784365</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.989047</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.236341</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.784365</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.989047</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.23638</v>
+        <v>3.9e-05</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.840503</v>
+        <v>0.056138</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.220608</v>
+        <v>0.231561</v>
       </c>
     </row>
     <row r="49">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">

--- a/output/pdf_financials_xlsx/SAGA.xlsx
+++ b/output/pdf_financials_xlsx/SAGA.xlsx
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>1.357053</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -4317,7 +4317,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs $</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>1.357053</v>
       </c>

--- a/output/pdf_financials_xlsx/SAGA.xlsx
+++ b/output/pdf_financials_xlsx/SAGA.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.073063</v>
+        <v>0.077594</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.318567</v>
+        <v>0.321683</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.575843</v>
+        <v>0.579197</v>
       </c>
     </row>
     <row r="8">
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.030696</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004283</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.091267</v>
       </c>
     </row>
     <row r="112">
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.030696</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004283</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.091267</v>
       </c>
     </row>
     <row r="135">
@@ -2625,13 +2625,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.107634</v>
+        <v>-0.13833</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.734814</v>
+        <v>-0.739097</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.238094</v>
+        <v>-3.329361</v>
       </c>
     </row>
   </sheetData>
@@ -3738,7 +3738,11 @@
           <t>Acquisition of equipment $</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>-0.030696</v>
       </c>
@@ -4770,7 +4774,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
         <v>0.004531</v>
       </c>
